--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20221.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20221.xlsx
@@ -465,19 +465,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -530,16 +530,19 @@
         <v>18</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>18</v>
       </c>
-      <c r="E2">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -592,19 +595,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
